--- a/inputdcspt_All.xlsx
+++ b/inputdcspt_All.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\JLM\Dropbox (Personal)\UNIVERSIDADE\GESTÃO\Direção DCSPT\DSD\questionario\dashboard_dcspt_publico_bundle\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D01F1D3F-F912-4B95-B90E-E67CE104DD35}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3CEA42EC-A1B1-413B-8EA0-63C8B94B3FC2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{1DBEFD56-9363-4F8B-ACC0-4EF6F1086AB3}"/>
   </bookViews>
@@ -950,7 +950,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="10">
+  <fills count="9">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -999,12 +999,6 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFF0000"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
   </fills>
   <borders count="2">
     <border>
@@ -1027,7 +1021,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
@@ -1049,7 +1043,6 @@
     <xf numFmtId="0" fontId="0" fillId="8" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1384,14 +1377,14 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{07EF0390-B0FA-4A65-BFBE-627208925094}">
-  <dimension ref="A1:AQ113"/>
+  <dimension ref="A1:AP113"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="55.6640625" bestFit="1" customWidth="1"/>
     <col min="3" max="8" width="8.77734375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:43" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:42" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1519,7 +1512,7 @@
         <v>259</v>
       </c>
     </row>
-    <row r="2" spans="1:43" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:42" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>9</v>
       </c>
@@ -1644,12 +1637,8 @@
       <c r="AP2">
         <v>2</v>
       </c>
-      <c r="AQ2">
-        <f>+SUM(J2:AK2)</f>
-        <v>70</v>
-      </c>
     </row>
-    <row r="3" spans="1:43" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:42" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>15</v>
       </c>
@@ -1774,12 +1763,8 @@
       <c r="AP3">
         <v>5</v>
       </c>
-      <c r="AQ3">
-        <f t="shared" ref="AQ3:AQ66" si="0">+SUM(J3:AK3)</f>
-        <v>64</v>
-      </c>
     </row>
-    <row r="4" spans="1:43" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:42" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>20</v>
       </c>
@@ -1904,12 +1889,8 @@
       <c r="AP4">
         <v>1</v>
       </c>
-      <c r="AQ4">
-        <f t="shared" si="0"/>
-        <v>42</v>
-      </c>
     </row>
-    <row r="5" spans="1:43" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:42" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>24</v>
       </c>
@@ -2034,12 +2015,8 @@
       <c r="AP5">
         <v>5</v>
       </c>
-      <c r="AQ5">
-        <f t="shared" si="0"/>
-        <v>57</v>
-      </c>
     </row>
-    <row r="6" spans="1:43" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:42" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>27</v>
       </c>
@@ -2164,12 +2141,8 @@
       <c r="AP6">
         <v>3</v>
       </c>
-      <c r="AQ6">
-        <f t="shared" si="0"/>
-        <v>57</v>
-      </c>
     </row>
-    <row r="7" spans="1:43" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:42" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>30</v>
       </c>
@@ -2294,12 +2267,8 @@
       <c r="AP7">
         <v>5</v>
       </c>
-      <c r="AQ7">
-        <f t="shared" si="0"/>
-        <v>32</v>
-      </c>
     </row>
-    <row r="8" spans="1:43" s="10" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:42" s="10" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A8" s="10" t="s">
         <v>33</v>
       </c>
@@ -2424,12 +2393,8 @@
       <c r="AP8" s="10">
         <v>3</v>
       </c>
-      <c r="AQ8" s="10">
-        <f t="shared" si="0"/>
-        <v>30</v>
-      </c>
     </row>
-    <row r="9" spans="1:43" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:42" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>36</v>
       </c>
@@ -2554,12 +2519,8 @@
       <c r="AP9">
         <v>5</v>
       </c>
-      <c r="AQ9">
-        <f t="shared" si="0"/>
-        <v>32</v>
-      </c>
     </row>
-    <row r="10" spans="1:43" s="10" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:42" s="10" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A10" s="10" t="s">
         <v>38</v>
       </c>
@@ -2684,12 +2645,8 @@
       <c r="AP10" s="10">
         <v>3</v>
       </c>
-      <c r="AQ10" s="10">
-        <f t="shared" si="0"/>
-        <v>29</v>
-      </c>
     </row>
-    <row r="11" spans="1:43" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:42" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>41</v>
       </c>
@@ -2814,12 +2771,8 @@
       <c r="AP11">
         <v>2</v>
       </c>
-      <c r="AQ11">
-        <f t="shared" si="0"/>
-        <v>57</v>
-      </c>
     </row>
-    <row r="12" spans="1:43" s="10" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:42" s="10" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A12" s="10" t="s">
         <v>43</v>
       </c>
@@ -2946,12 +2899,8 @@
       <c r="AP12" s="10">
         <v>3</v>
       </c>
-      <c r="AQ12" s="10">
-        <f t="shared" si="0"/>
-        <v>45</v>
-      </c>
     </row>
-    <row r="13" spans="1:43" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:42" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>48</v>
       </c>
@@ -3076,12 +3025,8 @@
       <c r="AP13">
         <v>4</v>
       </c>
-      <c r="AQ13">
-        <f t="shared" si="0"/>
-        <v>61</v>
-      </c>
     </row>
-    <row r="14" spans="1:43" s="10" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:42" s="10" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A14" s="10" t="s">
         <v>50</v>
       </c>
@@ -3204,12 +3149,8 @@
       <c r="AP14" s="10">
         <v>1</v>
       </c>
-      <c r="AQ14" s="10">
-        <f t="shared" si="0"/>
-        <v>41</v>
-      </c>
     </row>
-    <row r="15" spans="1:43" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:42" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>53</v>
       </c>
@@ -3334,12 +3275,8 @@
       <c r="AP15">
         <v>1</v>
       </c>
-      <c r="AQ15">
-        <f t="shared" si="0"/>
-        <v>46</v>
-      </c>
     </row>
-    <row r="16" spans="1:43" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:42" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
         <v>56</v>
       </c>
@@ -3464,12 +3401,8 @@
       <c r="AP16">
         <v>3</v>
       </c>
-      <c r="AQ16">
-        <f t="shared" si="0"/>
-        <v>60</v>
-      </c>
     </row>
-    <row r="17" spans="1:43" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:42" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
         <v>58</v>
       </c>
@@ -3594,12 +3527,8 @@
       <c r="AP17">
         <v>2</v>
       </c>
-      <c r="AQ17">
-        <f t="shared" si="0"/>
-        <v>59</v>
-      </c>
     </row>
-    <row r="18" spans="1:43" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:42" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
         <v>60</v>
       </c>
@@ -3724,12 +3653,8 @@
       <c r="AP18">
         <v>4</v>
       </c>
-      <c r="AQ18">
-        <f t="shared" si="0"/>
-        <v>63</v>
-      </c>
     </row>
-    <row r="19" spans="1:43" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:42" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
         <v>62</v>
       </c>
@@ -3854,12 +3779,8 @@
       <c r="AP19">
         <v>1</v>
       </c>
-      <c r="AQ19">
-        <f t="shared" si="0"/>
-        <v>35</v>
-      </c>
     </row>
-    <row r="20" spans="1:43" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:42" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
         <v>65</v>
       </c>
@@ -3984,12 +3905,8 @@
       <c r="AP20">
         <v>4</v>
       </c>
-      <c r="AQ20">
-        <f t="shared" si="0"/>
-        <v>44</v>
-      </c>
     </row>
-    <row r="21" spans="1:43" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:42" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
         <v>67</v>
       </c>
@@ -4114,12 +4031,8 @@
       <c r="AP21">
         <v>4</v>
       </c>
-      <c r="AQ21">
-        <f t="shared" si="0"/>
-        <v>52</v>
-      </c>
     </row>
-    <row r="22" spans="1:43" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:42" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
         <v>69</v>
       </c>
@@ -4244,12 +4157,8 @@
       <c r="AP22">
         <v>5</v>
       </c>
-      <c r="AQ22">
-        <f t="shared" si="0"/>
-        <v>46</v>
-      </c>
     </row>
-    <row r="23" spans="1:43" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:42" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
         <v>71</v>
       </c>
@@ -4374,12 +4283,8 @@
       <c r="AP23">
         <v>1</v>
       </c>
-      <c r="AQ23">
-        <f t="shared" si="0"/>
-        <v>43</v>
-      </c>
     </row>
-    <row r="24" spans="1:43" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:42" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
         <v>73</v>
       </c>
@@ -4504,12 +4409,8 @@
       <c r="AP24">
         <v>2</v>
       </c>
-      <c r="AQ24">
-        <f t="shared" si="0"/>
-        <v>45</v>
-      </c>
     </row>
-    <row r="25" spans="1:43" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:42" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
         <v>75</v>
       </c>
@@ -4634,12 +4535,8 @@
       <c r="AP25">
         <v>4</v>
       </c>
-      <c r="AQ25">
-        <f t="shared" si="0"/>
-        <v>31</v>
-      </c>
     </row>
-    <row r="26" spans="1:43" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:42" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
         <v>77</v>
       </c>
@@ -4764,12 +4661,8 @@
       <c r="AP26">
         <v>1</v>
       </c>
-      <c r="AQ26">
-        <f t="shared" si="0"/>
-        <v>76</v>
-      </c>
     </row>
-    <row r="27" spans="1:43" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:42" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
         <v>80</v>
       </c>
@@ -4894,12 +4787,8 @@
       <c r="AP27">
         <v>2</v>
       </c>
-      <c r="AQ27">
-        <f t="shared" si="0"/>
-        <v>78</v>
-      </c>
     </row>
-    <row r="28" spans="1:43" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:42" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
         <v>82</v>
       </c>
@@ -5024,12 +4913,8 @@
       <c r="AP28">
         <v>1</v>
       </c>
-      <c r="AQ28">
-        <f t="shared" si="0"/>
-        <v>62</v>
-      </c>
     </row>
-    <row r="29" spans="1:43" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:42" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
         <v>84</v>
       </c>
@@ -5154,12 +5039,8 @@
       <c r="AP29">
         <v>3</v>
       </c>
-      <c r="AQ29">
-        <f t="shared" si="0"/>
-        <v>62</v>
-      </c>
     </row>
-    <row r="30" spans="1:43" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:42" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
         <v>86</v>
       </c>
@@ -5284,12 +5165,8 @@
       <c r="AP30">
         <v>2</v>
       </c>
-      <c r="AQ30">
-        <f t="shared" si="0"/>
-        <v>48</v>
-      </c>
     </row>
-    <row r="31" spans="1:43" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:42" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
         <v>88</v>
       </c>
@@ -5414,12 +5291,8 @@
       <c r="AP31">
         <v>3</v>
       </c>
-      <c r="AQ31">
-        <f t="shared" si="0"/>
-        <v>51</v>
-      </c>
     </row>
-    <row r="32" spans="1:43" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:42" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
         <v>90</v>
       </c>
@@ -5544,12 +5417,8 @@
       <c r="AP32">
         <v>1</v>
       </c>
-      <c r="AQ32">
-        <f t="shared" si="0"/>
-        <v>50</v>
-      </c>
     </row>
-    <row r="33" spans="1:43" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:42" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
         <v>92</v>
       </c>
@@ -5674,12 +5543,8 @@
       <c r="AP33">
         <v>2</v>
       </c>
-      <c r="AQ33">
-        <f t="shared" si="0"/>
-        <v>42</v>
-      </c>
     </row>
-    <row r="34" spans="1:43" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:42" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
         <v>94</v>
       </c>
@@ -5804,12 +5669,8 @@
       <c r="AP34">
         <v>2</v>
       </c>
-      <c r="AQ34">
-        <f t="shared" si="0"/>
-        <v>46</v>
-      </c>
     </row>
-    <row r="35" spans="1:43" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:42" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
         <v>96</v>
       </c>
@@ -5934,12 +5795,8 @@
       <c r="AP35">
         <v>2</v>
       </c>
-      <c r="AQ35">
-        <f t="shared" si="0"/>
-        <v>41</v>
-      </c>
     </row>
-    <row r="36" spans="1:43" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:42" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
         <v>98</v>
       </c>
@@ -6064,12 +5921,8 @@
       <c r="AP36">
         <v>3</v>
       </c>
-      <c r="AQ36">
-        <f t="shared" si="0"/>
-        <v>59</v>
-      </c>
     </row>
-    <row r="37" spans="1:43" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:42" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
         <v>100</v>
       </c>
@@ -6194,12 +6047,8 @@
       <c r="AP37">
         <v>1</v>
       </c>
-      <c r="AQ37">
-        <f t="shared" si="0"/>
-        <v>59</v>
-      </c>
     </row>
-    <row r="38" spans="1:43" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:42" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
         <v>102</v>
       </c>
@@ -6324,12 +6173,8 @@
       <c r="AP38">
         <v>3</v>
       </c>
-      <c r="AQ38">
-        <f t="shared" si="0"/>
-        <v>44</v>
-      </c>
     </row>
-    <row r="39" spans="1:43" s="10" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:42" s="10" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A39" s="10" t="s">
         <v>104</v>
       </c>
@@ -6454,12 +6299,8 @@
       <c r="AP39" s="10">
         <v>1</v>
       </c>
-      <c r="AQ39" s="10">
-        <f t="shared" si="0"/>
-        <v>46</v>
-      </c>
     </row>
-    <row r="40" spans="1:43" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:42" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
         <v>107</v>
       </c>
@@ -6584,12 +6425,8 @@
       <c r="AP40">
         <v>1</v>
       </c>
-      <c r="AQ40">
-        <f t="shared" si="0"/>
-        <v>73</v>
-      </c>
     </row>
-    <row r="41" spans="1:43" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:42" x14ac:dyDescent="0.3">
       <c r="A41" t="s">
         <v>109</v>
       </c>
@@ -6714,12 +6551,8 @@
       <c r="AP41">
         <v>2</v>
       </c>
-      <c r="AQ41">
-        <f t="shared" si="0"/>
-        <v>80</v>
-      </c>
     </row>
-    <row r="42" spans="1:43" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:42" x14ac:dyDescent="0.3">
       <c r="A42" t="s">
         <v>111</v>
       </c>
@@ -6844,12 +6677,8 @@
       <c r="AP42">
         <v>1</v>
       </c>
-      <c r="AQ42">
-        <f t="shared" si="0"/>
-        <v>58</v>
-      </c>
     </row>
-    <row r="43" spans="1:43" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:42" x14ac:dyDescent="0.3">
       <c r="A43" t="s">
         <v>113</v>
       </c>
@@ -6974,12 +6803,8 @@
       <c r="AP43">
         <v>1</v>
       </c>
-      <c r="AQ43">
-        <f t="shared" si="0"/>
-        <v>70</v>
-      </c>
     </row>
-    <row r="44" spans="1:43" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:42" x14ac:dyDescent="0.3">
       <c r="A44" t="s">
         <v>115</v>
       </c>
@@ -7104,12 +6929,8 @@
       <c r="AP44">
         <v>1</v>
       </c>
-      <c r="AQ44">
-        <f t="shared" si="0"/>
-        <v>43</v>
-      </c>
     </row>
-    <row r="45" spans="1:43" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:42" x14ac:dyDescent="0.3">
       <c r="A45" t="s">
         <v>117</v>
       </c>
@@ -7234,12 +7055,8 @@
       <c r="AP45">
         <v>1</v>
       </c>
-      <c r="AQ45">
-        <f t="shared" si="0"/>
-        <v>48</v>
-      </c>
     </row>
-    <row r="46" spans="1:43" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:42" x14ac:dyDescent="0.3">
       <c r="A46" t="s">
         <v>119</v>
       </c>
@@ -7364,12 +7181,8 @@
       <c r="AP46">
         <v>1</v>
       </c>
-      <c r="AQ46">
-        <f t="shared" si="0"/>
-        <v>46</v>
-      </c>
     </row>
-    <row r="47" spans="1:43" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:42" x14ac:dyDescent="0.3">
       <c r="A47" t="s">
         <v>121</v>
       </c>
@@ -7494,12 +7307,8 @@
       <c r="AP47">
         <v>3</v>
       </c>
-      <c r="AQ47">
-        <f t="shared" si="0"/>
-        <v>57</v>
-      </c>
     </row>
-    <row r="48" spans="1:43" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:42" x14ac:dyDescent="0.3">
       <c r="A48" t="s">
         <v>123</v>
       </c>
@@ -7624,12 +7433,8 @@
       <c r="AP48">
         <v>1</v>
       </c>
-      <c r="AQ48">
-        <f t="shared" si="0"/>
-        <v>39</v>
-      </c>
     </row>
-    <row r="49" spans="1:43" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:42" x14ac:dyDescent="0.3">
       <c r="A49" t="s">
         <v>125</v>
       </c>
@@ -7754,12 +7559,8 @@
       <c r="AP49">
         <v>1</v>
       </c>
-      <c r="AQ49">
-        <f t="shared" si="0"/>
-        <v>45</v>
-      </c>
     </row>
-    <row r="50" spans="1:43" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:42" x14ac:dyDescent="0.3">
       <c r="A50" t="s">
         <v>127</v>
       </c>
@@ -7884,12 +7685,8 @@
       <c r="AP50">
         <v>1</v>
       </c>
-      <c r="AQ50">
-        <f t="shared" si="0"/>
-        <v>51</v>
-      </c>
     </row>
-    <row r="51" spans="1:43" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:42" x14ac:dyDescent="0.3">
       <c r="A51" t="s">
         <v>129</v>
       </c>
@@ -8014,12 +7811,8 @@
       <c r="AP51">
         <v>3</v>
       </c>
-      <c r="AQ51">
-        <f t="shared" si="0"/>
-        <v>70</v>
-      </c>
     </row>
-    <row r="52" spans="1:43" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:42" x14ac:dyDescent="0.3">
       <c r="A52" t="s">
         <v>131</v>
       </c>
@@ -8144,12 +7937,8 @@
       <c r="AP52">
         <v>3</v>
       </c>
-      <c r="AQ52">
-        <f t="shared" si="0"/>
-        <v>35</v>
-      </c>
     </row>
-    <row r="53" spans="1:43" s="10" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:42" s="10" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A53" s="10" t="s">
         <v>133</v>
       </c>
@@ -8274,12 +8063,8 @@
       <c r="AP53" s="10">
         <v>1</v>
       </c>
-      <c r="AQ53" s="10">
-        <f t="shared" si="0"/>
-        <v>40</v>
-      </c>
     </row>
-    <row r="54" spans="1:43" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:42" x14ac:dyDescent="0.3">
       <c r="A54" t="s">
         <v>136</v>
       </c>
@@ -8404,12 +8189,8 @@
       <c r="AP54">
         <v>3</v>
       </c>
-      <c r="AQ54">
-        <f t="shared" si="0"/>
-        <v>50</v>
-      </c>
     </row>
-    <row r="55" spans="1:43" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:42" x14ac:dyDescent="0.3">
       <c r="A55" t="s">
         <v>138</v>
       </c>
@@ -8534,12 +8315,8 @@
       <c r="AP55">
         <v>1</v>
       </c>
-      <c r="AQ55">
-        <f t="shared" si="0"/>
-        <v>45</v>
-      </c>
     </row>
-    <row r="56" spans="1:43" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:42" x14ac:dyDescent="0.3">
       <c r="A56" t="s">
         <v>140</v>
       </c>
@@ -8664,12 +8441,8 @@
       <c r="AP56">
         <v>1</v>
       </c>
-      <c r="AQ56">
-        <f t="shared" si="0"/>
-        <v>53</v>
-      </c>
     </row>
-    <row r="57" spans="1:43" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:42" x14ac:dyDescent="0.3">
       <c r="A57" t="s">
         <v>142</v>
       </c>
@@ -8794,12 +8567,8 @@
       <c r="AP57">
         <v>1</v>
       </c>
-      <c r="AQ57">
-        <f t="shared" si="0"/>
-        <v>54</v>
-      </c>
     </row>
-    <row r="58" spans="1:43" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:42" x14ac:dyDescent="0.3">
       <c r="A58" t="s">
         <v>144</v>
       </c>
@@ -8924,12 +8693,8 @@
       <c r="AP58">
         <v>3</v>
       </c>
-      <c r="AQ58">
-        <f t="shared" si="0"/>
-        <v>47</v>
-      </c>
     </row>
-    <row r="59" spans="1:43" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:42" x14ac:dyDescent="0.3">
       <c r="A59" t="s">
         <v>146</v>
       </c>
@@ -9054,12 +8819,8 @@
       <c r="AP59">
         <v>3</v>
       </c>
-      <c r="AQ59">
-        <f t="shared" si="0"/>
-        <v>45</v>
-      </c>
     </row>
-    <row r="60" spans="1:43" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:42" x14ac:dyDescent="0.3">
       <c r="A60" t="s">
         <v>148</v>
       </c>
@@ -9184,12 +8945,8 @@
       <c r="AP60">
         <v>1</v>
       </c>
-      <c r="AQ60">
-        <f t="shared" si="0"/>
-        <v>48</v>
-      </c>
     </row>
-    <row r="61" spans="1:43" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:42" x14ac:dyDescent="0.3">
       <c r="A61" t="s">
         <v>150</v>
       </c>
@@ -9314,12 +9071,8 @@
       <c r="AP61">
         <v>1</v>
       </c>
-      <c r="AQ61">
-        <f t="shared" si="0"/>
-        <v>57</v>
-      </c>
     </row>
-    <row r="62" spans="1:43" s="10" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:42" s="10" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A62" s="10" t="s">
         <v>152</v>
       </c>
@@ -9444,12 +9197,8 @@
       <c r="AP62" s="10">
         <v>4</v>
       </c>
-      <c r="AQ62" s="10">
-        <f t="shared" si="0"/>
-        <v>30</v>
-      </c>
     </row>
-    <row r="63" spans="1:43" s="10" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:42" s="10" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A63" s="10" t="s">
         <v>154</v>
       </c>
@@ -9574,12 +9323,8 @@
       <c r="AP63" s="10">
         <v>3</v>
       </c>
-      <c r="AQ63" s="10">
-        <f t="shared" si="0"/>
-        <v>29</v>
-      </c>
     </row>
-    <row r="64" spans="1:43" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:42" x14ac:dyDescent="0.3">
       <c r="A64" t="s">
         <v>156</v>
       </c>
@@ -9704,12 +9449,8 @@
       <c r="AP64">
         <v>5</v>
       </c>
-      <c r="AQ64">
-        <f t="shared" si="0"/>
-        <v>32</v>
-      </c>
     </row>
-    <row r="65" spans="1:43" s="10" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:42" s="10" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A65" s="10" t="s">
         <v>158</v>
       </c>
@@ -9836,12 +9577,8 @@
       <c r="AP65" s="10">
         <v>1</v>
       </c>
-      <c r="AQ65" s="10">
-        <f t="shared" si="0"/>
-        <v>37</v>
-      </c>
     </row>
-    <row r="66" spans="1:43" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:42" x14ac:dyDescent="0.3">
       <c r="A66" t="s">
         <v>160</v>
       </c>
@@ -9966,12 +9703,8 @@
       <c r="AP66">
         <v>3</v>
       </c>
-      <c r="AQ66">
-        <f t="shared" si="0"/>
-        <v>50</v>
-      </c>
     </row>
-    <row r="67" spans="1:43" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:42" x14ac:dyDescent="0.3">
       <c r="A67" t="s">
         <v>162</v>
       </c>
@@ -10096,12 +9829,8 @@
       <c r="AP67">
         <v>4</v>
       </c>
-      <c r="AQ67">
-        <f t="shared" ref="AQ67:AQ112" si="1">+SUM(J67:AK67)</f>
-        <v>59</v>
-      </c>
     </row>
-    <row r="68" spans="1:43" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:42" x14ac:dyDescent="0.3">
       <c r="A68" t="s">
         <v>164</v>
       </c>
@@ -10226,12 +9955,8 @@
       <c r="AP68">
         <v>1</v>
       </c>
-      <c r="AQ68">
-        <f t="shared" si="1"/>
-        <v>42</v>
-      </c>
     </row>
-    <row r="69" spans="1:43" s="10" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:42" s="10" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A69" s="10" t="s">
         <v>166</v>
       </c>
@@ -10358,12 +10083,8 @@
       <c r="AP69" s="10">
         <v>3</v>
       </c>
-      <c r="AQ69" s="10">
-        <f t="shared" si="1"/>
-        <v>38</v>
-      </c>
     </row>
-    <row r="70" spans="1:43" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:42" x14ac:dyDescent="0.3">
       <c r="A70" t="s">
         <v>168</v>
       </c>
@@ -10488,12 +10209,8 @@
       <c r="AP70">
         <v>3</v>
       </c>
-      <c r="AQ70">
-        <f t="shared" si="1"/>
-        <v>65</v>
-      </c>
     </row>
-    <row r="71" spans="1:43" x14ac:dyDescent="0.3">
+    <row r="71" spans="1:42" x14ac:dyDescent="0.3">
       <c r="A71" t="s">
         <v>170</v>
       </c>
@@ -10618,12 +10335,8 @@
       <c r="AP71">
         <v>4</v>
       </c>
-      <c r="AQ71">
-        <f t="shared" si="1"/>
-        <v>57</v>
-      </c>
     </row>
-    <row r="72" spans="1:43" s="10" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="72" spans="1:42" s="10" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A72" s="10" t="s">
         <v>172</v>
       </c>
@@ -10748,12 +10461,8 @@
       <c r="AP72" s="10">
         <v>4</v>
       </c>
-      <c r="AQ72" s="10">
-        <f t="shared" si="1"/>
-        <v>43</v>
-      </c>
     </row>
-    <row r="73" spans="1:43" x14ac:dyDescent="0.3">
+    <row r="73" spans="1:42" x14ac:dyDescent="0.3">
       <c r="A73" t="s">
         <v>175</v>
       </c>
@@ -10878,12 +10587,8 @@
       <c r="AP73">
         <v>3</v>
       </c>
-      <c r="AQ73">
-        <f t="shared" si="1"/>
-        <v>41</v>
-      </c>
     </row>
-    <row r="74" spans="1:43" x14ac:dyDescent="0.3">
+    <row r="74" spans="1:42" x14ac:dyDescent="0.3">
       <c r="A74" t="s">
         <v>177</v>
       </c>
@@ -11008,12 +10713,8 @@
       <c r="AP74">
         <v>3</v>
       </c>
-      <c r="AQ74">
-        <f t="shared" si="1"/>
-        <v>46</v>
-      </c>
     </row>
-    <row r="75" spans="1:43" x14ac:dyDescent="0.3">
+    <row r="75" spans="1:42" x14ac:dyDescent="0.3">
       <c r="A75" t="s">
         <v>179</v>
       </c>
@@ -11138,12 +10839,8 @@
       <c r="AP75">
         <v>2</v>
       </c>
-      <c r="AQ75">
-        <f t="shared" si="1"/>
-        <v>39</v>
-      </c>
     </row>
-    <row r="76" spans="1:43" x14ac:dyDescent="0.3">
+    <row r="76" spans="1:42" x14ac:dyDescent="0.3">
       <c r="A76" t="s">
         <v>181</v>
       </c>
@@ -11268,12 +10965,8 @@
       <c r="AP76">
         <v>1</v>
       </c>
-      <c r="AQ76">
-        <f t="shared" si="1"/>
-        <v>63</v>
-      </c>
     </row>
-    <row r="77" spans="1:43" x14ac:dyDescent="0.3">
+    <row r="77" spans="1:42" x14ac:dyDescent="0.3">
       <c r="A77" t="s">
         <v>183</v>
       </c>
@@ -11398,12 +11091,8 @@
       <c r="AP77">
         <v>3</v>
       </c>
-      <c r="AQ77">
-        <f t="shared" si="1"/>
-        <v>68</v>
-      </c>
     </row>
-    <row r="78" spans="1:43" x14ac:dyDescent="0.3">
+    <row r="78" spans="1:42" x14ac:dyDescent="0.3">
       <c r="A78" t="s">
         <v>185</v>
       </c>
@@ -11528,12 +11217,8 @@
       <c r="AP78">
         <v>1</v>
       </c>
-      <c r="AQ78">
-        <f t="shared" si="1"/>
-        <v>73</v>
-      </c>
     </row>
-    <row r="79" spans="1:43" x14ac:dyDescent="0.3">
+    <row r="79" spans="1:42" x14ac:dyDescent="0.3">
       <c r="A79" t="s">
         <v>187</v>
       </c>
@@ -11658,12 +11343,8 @@
       <c r="AP79">
         <v>4</v>
       </c>
-      <c r="AQ79">
-        <f t="shared" si="1"/>
-        <v>55</v>
-      </c>
     </row>
-    <row r="80" spans="1:43" x14ac:dyDescent="0.3">
+    <row r="80" spans="1:42" x14ac:dyDescent="0.3">
       <c r="A80" t="s">
         <v>189</v>
       </c>
@@ -11788,12 +11469,8 @@
       <c r="AP80">
         <v>1</v>
       </c>
-      <c r="AQ80">
-        <f t="shared" si="1"/>
-        <v>37</v>
-      </c>
     </row>
-    <row r="81" spans="1:43" x14ac:dyDescent="0.3">
+    <row r="81" spans="1:42" x14ac:dyDescent="0.3">
       <c r="A81" t="s">
         <v>191</v>
       </c>
@@ -11918,12 +11595,8 @@
       <c r="AP81">
         <v>1</v>
       </c>
-      <c r="AQ81">
-        <f t="shared" si="1"/>
-        <v>46</v>
-      </c>
     </row>
-    <row r="82" spans="1:43" x14ac:dyDescent="0.3">
+    <row r="82" spans="1:42" x14ac:dyDescent="0.3">
       <c r="A82" t="s">
         <v>193</v>
       </c>
@@ -12048,12 +11721,8 @@
       <c r="AP82">
         <v>2</v>
       </c>
-      <c r="AQ82">
-        <f t="shared" si="1"/>
-        <v>63</v>
-      </c>
     </row>
-    <row r="83" spans="1:43" x14ac:dyDescent="0.3">
+    <row r="83" spans="1:42" x14ac:dyDescent="0.3">
       <c r="A83" t="s">
         <v>195</v>
       </c>
@@ -12178,12 +11847,8 @@
       <c r="AP83">
         <v>3</v>
       </c>
-      <c r="AQ83">
-        <f t="shared" si="1"/>
-        <v>44</v>
-      </c>
     </row>
-    <row r="84" spans="1:43" s="10" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="84" spans="1:42" s="10" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A84" s="10" t="s">
         <v>197</v>
       </c>
@@ -12308,12 +11973,8 @@
       <c r="AP84" s="10">
         <v>4</v>
       </c>
-      <c r="AQ84" s="10">
-        <f t="shared" si="1"/>
-        <v>50</v>
-      </c>
     </row>
-    <row r="85" spans="1:43" x14ac:dyDescent="0.3">
+    <row r="85" spans="1:42" x14ac:dyDescent="0.3">
       <c r="A85" t="s">
         <v>200</v>
       </c>
@@ -12438,12 +12099,8 @@
       <c r="AP85">
         <v>5</v>
       </c>
-      <c r="AQ85">
-        <f t="shared" si="1"/>
-        <v>44</v>
-      </c>
     </row>
-    <row r="86" spans="1:43" x14ac:dyDescent="0.3">
+    <row r="86" spans="1:42" x14ac:dyDescent="0.3">
       <c r="A86" t="s">
         <v>202</v>
       </c>
@@ -12568,12 +12225,8 @@
       <c r="AP86">
         <v>3</v>
       </c>
-      <c r="AQ86">
-        <f t="shared" si="1"/>
-        <v>44</v>
-      </c>
     </row>
-    <row r="87" spans="1:43" x14ac:dyDescent="0.3">
+    <row r="87" spans="1:42" x14ac:dyDescent="0.3">
       <c r="A87" t="s">
         <v>204</v>
       </c>
@@ -12698,12 +12351,8 @@
       <c r="AP87">
         <v>1</v>
       </c>
-      <c r="AQ87">
-        <f t="shared" si="1"/>
-        <v>50</v>
-      </c>
     </row>
-    <row r="88" spans="1:43" x14ac:dyDescent="0.3">
+    <row r="88" spans="1:42" x14ac:dyDescent="0.3">
       <c r="A88" t="s">
         <v>206</v>
       </c>
@@ -12828,12 +12477,8 @@
       <c r="AP88">
         <v>3</v>
       </c>
-      <c r="AQ88">
-        <f t="shared" si="1"/>
-        <v>47</v>
-      </c>
     </row>
-    <row r="89" spans="1:43" x14ac:dyDescent="0.3">
+    <row r="89" spans="1:42" x14ac:dyDescent="0.3">
       <c r="A89" t="s">
         <v>208</v>
       </c>
@@ -12958,12 +12603,8 @@
       <c r="AP89">
         <v>2</v>
       </c>
-      <c r="AQ89">
-        <f t="shared" si="1"/>
-        <v>46</v>
-      </c>
     </row>
-    <row r="90" spans="1:43" x14ac:dyDescent="0.3">
+    <row r="90" spans="1:42" x14ac:dyDescent="0.3">
       <c r="A90" t="s">
         <v>210</v>
       </c>
@@ -13088,12 +12729,8 @@
       <c r="AP90">
         <v>3</v>
       </c>
-      <c r="AQ90">
-        <f t="shared" si="1"/>
-        <v>44</v>
-      </c>
     </row>
-    <row r="91" spans="1:43" x14ac:dyDescent="0.3">
+    <row r="91" spans="1:42" x14ac:dyDescent="0.3">
       <c r="A91" t="s">
         <v>212</v>
       </c>
@@ -13218,12 +12855,8 @@
       <c r="AP91">
         <v>1</v>
       </c>
-      <c r="AQ91">
-        <f t="shared" si="1"/>
-        <v>44</v>
-      </c>
     </row>
-    <row r="92" spans="1:43" x14ac:dyDescent="0.3">
+    <row r="92" spans="1:42" x14ac:dyDescent="0.3">
       <c r="A92" t="s">
         <v>214</v>
       </c>
@@ -13348,12 +12981,8 @@
       <c r="AP92">
         <v>1</v>
       </c>
-      <c r="AQ92">
-        <f t="shared" si="1"/>
-        <v>52</v>
-      </c>
     </row>
-    <row r="93" spans="1:43" x14ac:dyDescent="0.3">
+    <row r="93" spans="1:42" x14ac:dyDescent="0.3">
       <c r="A93" t="s">
         <v>216</v>
       </c>
@@ -13478,12 +13107,8 @@
       <c r="AP93">
         <v>1</v>
       </c>
-      <c r="AQ93">
-        <f t="shared" si="1"/>
-        <v>47</v>
-      </c>
     </row>
-    <row r="94" spans="1:43" x14ac:dyDescent="0.3">
+    <row r="94" spans="1:42" x14ac:dyDescent="0.3">
       <c r="A94" t="s">
         <v>218</v>
       </c>
@@ -13608,12 +13233,8 @@
       <c r="AP94">
         <v>1</v>
       </c>
-      <c r="AQ94">
-        <f t="shared" si="1"/>
-        <v>44</v>
-      </c>
     </row>
-    <row r="95" spans="1:43" x14ac:dyDescent="0.3">
+    <row r="95" spans="1:42" x14ac:dyDescent="0.3">
       <c r="A95" t="s">
         <v>220</v>
       </c>
@@ -13738,12 +13359,8 @@
       <c r="AP95">
         <v>2</v>
       </c>
-      <c r="AQ95">
-        <f t="shared" si="1"/>
-        <v>67</v>
-      </c>
     </row>
-    <row r="96" spans="1:43" x14ac:dyDescent="0.3">
+    <row r="96" spans="1:42" x14ac:dyDescent="0.3">
       <c r="A96" t="s">
         <v>222</v>
       </c>
@@ -13868,12 +13485,8 @@
       <c r="AP96">
         <v>1</v>
       </c>
-      <c r="AQ96">
-        <f t="shared" si="1"/>
-        <v>57</v>
-      </c>
     </row>
-    <row r="97" spans="1:43" x14ac:dyDescent="0.3">
+    <row r="97" spans="1:42" x14ac:dyDescent="0.3">
       <c r="A97" t="s">
         <v>224</v>
       </c>
@@ -13998,12 +13611,8 @@
       <c r="AP97">
         <v>1</v>
       </c>
-      <c r="AQ97">
-        <f t="shared" si="1"/>
-        <v>54</v>
-      </c>
     </row>
-    <row r="98" spans="1:43" s="10" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="98" spans="1:42" s="10" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A98" s="10" t="s">
         <v>226</v>
       </c>
@@ -14128,12 +13737,8 @@
       <c r="AP98" s="10">
         <v>3</v>
       </c>
-      <c r="AQ98" s="13">
-        <f t="shared" si="1"/>
-        <v>29</v>
-      </c>
     </row>
-    <row r="99" spans="1:43" x14ac:dyDescent="0.3">
+    <row r="99" spans="1:42" x14ac:dyDescent="0.3">
       <c r="A99" t="s">
         <v>228</v>
       </c>
@@ -14258,12 +13863,8 @@
       <c r="AP99">
         <v>3</v>
       </c>
-      <c r="AQ99">
-        <f t="shared" si="1"/>
-        <v>39</v>
-      </c>
     </row>
-    <row r="100" spans="1:43" x14ac:dyDescent="0.3">
+    <row r="100" spans="1:42" x14ac:dyDescent="0.3">
       <c r="A100" t="s">
         <v>230</v>
       </c>
@@ -14388,12 +13989,8 @@
       <c r="AP100">
         <v>1</v>
       </c>
-      <c r="AQ100">
-        <f t="shared" si="1"/>
-        <v>40</v>
-      </c>
     </row>
-    <row r="101" spans="1:43" x14ac:dyDescent="0.3">
+    <row r="101" spans="1:42" x14ac:dyDescent="0.3">
       <c r="A101" t="s">
         <v>232</v>
       </c>
@@ -14518,12 +14115,8 @@
       <c r="AP101">
         <v>1</v>
       </c>
-      <c r="AQ101">
-        <f t="shared" si="1"/>
-        <v>55</v>
-      </c>
     </row>
-    <row r="102" spans="1:43" x14ac:dyDescent="0.3">
+    <row r="102" spans="1:42" x14ac:dyDescent="0.3">
       <c r="A102" t="s">
         <v>234</v>
       </c>
@@ -14648,12 +14241,8 @@
       <c r="AP102">
         <v>1</v>
       </c>
-      <c r="AQ102">
-        <f t="shared" si="1"/>
-        <v>55</v>
-      </c>
     </row>
-    <row r="103" spans="1:43" x14ac:dyDescent="0.3">
+    <row r="103" spans="1:42" x14ac:dyDescent="0.3">
       <c r="A103" t="s">
         <v>236</v>
       </c>
@@ -14778,12 +14367,8 @@
       <c r="AP103">
         <v>1</v>
       </c>
-      <c r="AQ103">
-        <f t="shared" si="1"/>
-        <v>60</v>
-      </c>
     </row>
-    <row r="104" spans="1:43" x14ac:dyDescent="0.3">
+    <row r="104" spans="1:42" x14ac:dyDescent="0.3">
       <c r="A104" t="s">
         <v>238</v>
       </c>
@@ -14908,12 +14493,8 @@
       <c r="AP104">
         <v>1</v>
       </c>
-      <c r="AQ104">
-        <f t="shared" si="1"/>
-        <v>42</v>
-      </c>
     </row>
-    <row r="105" spans="1:43" s="10" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="105" spans="1:42" s="10" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A105" s="10" t="s">
         <v>240</v>
       </c>
@@ -15040,12 +14621,8 @@
       <c r="AP105" s="10">
         <v>2</v>
       </c>
-      <c r="AQ105" s="10">
-        <f t="shared" si="1"/>
-        <v>33</v>
-      </c>
     </row>
-    <row r="106" spans="1:43" x14ac:dyDescent="0.3">
+    <row r="106" spans="1:42" x14ac:dyDescent="0.3">
       <c r="A106" t="s">
         <v>243</v>
       </c>
@@ -15170,12 +14747,8 @@
       <c r="AP106">
         <v>3</v>
       </c>
-      <c r="AQ106">
-        <f t="shared" si="1"/>
-        <v>46</v>
-      </c>
     </row>
-    <row r="107" spans="1:43" x14ac:dyDescent="0.3">
+    <row r="107" spans="1:42" x14ac:dyDescent="0.3">
       <c r="A107" t="s">
         <v>245</v>
       </c>
@@ -15300,12 +14873,8 @@
       <c r="AP107">
         <v>4</v>
       </c>
-      <c r="AQ107">
-        <f t="shared" si="1"/>
-        <v>39</v>
-      </c>
     </row>
-    <row r="108" spans="1:43" x14ac:dyDescent="0.3">
+    <row r="108" spans="1:42" x14ac:dyDescent="0.3">
       <c r="A108" t="s">
         <v>247</v>
       </c>
@@ -15430,12 +14999,8 @@
       <c r="AP108">
         <v>1</v>
       </c>
-      <c r="AQ108">
-        <f t="shared" si="1"/>
-        <v>52</v>
-      </c>
     </row>
-    <row r="109" spans="1:43" x14ac:dyDescent="0.3">
+    <row r="109" spans="1:42" x14ac:dyDescent="0.3">
       <c r="A109" t="s">
         <v>249</v>
       </c>
@@ -15560,12 +15125,8 @@
       <c r="AP109">
         <v>2</v>
       </c>
-      <c r="AQ109">
-        <f t="shared" si="1"/>
-        <v>53</v>
-      </c>
     </row>
-    <row r="110" spans="1:43" x14ac:dyDescent="0.3">
+    <row r="110" spans="1:42" x14ac:dyDescent="0.3">
       <c r="A110" t="s">
         <v>251</v>
       </c>
@@ -15690,12 +15251,8 @@
       <c r="AP110">
         <v>4</v>
       </c>
-      <c r="AQ110">
-        <f t="shared" si="1"/>
-        <v>55</v>
-      </c>
     </row>
-    <row r="111" spans="1:43" x14ac:dyDescent="0.3">
+    <row r="111" spans="1:42" x14ac:dyDescent="0.3">
       <c r="A111" t="s">
         <v>253</v>
       </c>
@@ -15820,12 +15377,8 @@
       <c r="AP111">
         <v>3</v>
       </c>
-      <c r="AQ111">
-        <f t="shared" si="1"/>
-        <v>52</v>
-      </c>
     </row>
-    <row r="112" spans="1:43" s="10" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="112" spans="1:42" s="10" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A112" s="10" t="s">
         <v>255</v>
       </c>
@@ -15949,10 +15502,6 @@
       </c>
       <c r="AP112" s="10">
         <v>1</v>
-      </c>
-      <c r="AQ112" s="10">
-        <f t="shared" si="1"/>
-        <v>34</v>
       </c>
     </row>
     <row r="113" spans="1:42" x14ac:dyDescent="0.3">
